--- a/resources/raw/SESA592949_Week 1.xlsx
+++ b/resources/raw/SESA592949_Week 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schneiderelectric-my.sharepoint.com/personal/sesa450124_se_com/Documents/ALMA's back up files/MY FILES/AUDITS-TS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nomar Arboleda\OneDrive\Desktop\Python Project\KPI 1 - Quality Audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{A728A6CC-573A-40FB-B197-E948DCBEE594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED8BB0D6-7131-41F3-886C-DFA760B616BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF78369-50C3-486D-B9BD-175A0EBE7B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{23217799-04CE-4E18-BD47-5F2C8672298D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{23217799-04CE-4E18-BD47-5F2C8672298D}"/>
   </bookViews>
   <sheets>
     <sheet name="Technical" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="103">
   <si>
     <t>Agent Name:</t>
   </si>
@@ -354,12 +354,18 @@
   <si>
     <t>VIP Audit</t>
   </si>
+  <si>
+    <t>NC Arboleda</t>
+  </si>
+  <si>
+    <t>SESA592949</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,7 +721,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -889,6 +895,10 @@
     </xf>
     <xf numFmtId="10" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1057,9 +1067,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1097,7 +1107,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1203,7 +1213,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1345,7 +1355,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1354,42 +1364,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DF172B-A68A-47F5-BB92-9B91494F83D9}">
   <dimension ref="B2:G66"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="10"/>
-    <col min="2" max="2" width="41.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="88.5703125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="47.42578125" style="10" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="10"/>
+    <col min="1" max="1" width="8.86328125" style="10"/>
+    <col min="2" max="2" width="41.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.59765625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="16.86328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="47.3984375" style="10" customWidth="1"/>
+    <col min="8" max="16384" width="8.86328125" style="10"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="15" thickBot="1"/>
-    <row r="3" spans="2:7">
+    <row r="2" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="24"/>
+      <c r="C3" s="24" t="s">
+        <v>101</v>
+      </c>
       <c r="E3" s="54">
         <f>IF(D61="Yes",0%,IF(D61="No",F66))</f>
-        <v>0.95454545454545459</v>
+        <v>0.84090909090909094</v>
       </c>
       <c r="F3" s="55"/>
       <c r="G3" s="19"/>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="24"/>
+      <c r="C4" s="24" t="s">
+        <v>102</v>
+      </c>
       <c r="D4" s="23"/>
       <c r="E4" s="56"/>
       <c r="F4" s="57"/>
       <c r="G4" s="20"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B5" s="21" t="s">
         <v>2</v>
       </c>
@@ -1398,17 +1412,19 @@
       <c r="F5" s="57"/>
       <c r="G5" s="19"/>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B6" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="60">
+        <v>46023</v>
+      </c>
       <c r="D6" s="23"/>
       <c r="E6" s="56"/>
       <c r="F6" s="57"/>
       <c r="G6" s="20"/>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B7" s="21" t="s">
         <v>4</v>
       </c>
@@ -1418,7 +1434,7 @@
       <c r="F7" s="57"/>
       <c r="G7" s="20"/>
     </row>
-    <row r="8" spans="2:7" ht="15" thickBot="1">
+    <row r="8" spans="2:7" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="48" t="s">
         <v>5</v>
       </c>
@@ -1428,7 +1444,7 @@
       <c r="F8" s="59"/>
       <c r="G8" s="20"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B9" s="21" t="s">
         <v>6</v>
       </c>
@@ -1438,7 +1454,7 @@
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B10" s="21" t="s">
         <v>7</v>
       </c>
@@ -1448,7 +1464,7 @@
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B11" s="48" t="s">
         <v>8</v>
       </c>
@@ -1458,7 +1474,7 @@
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B12" s="12"/>
       <c r="C12" s="13"/>
       <c r="D12" s="11"/>
@@ -1466,7 +1482,7 @@
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B14" s="53" t="s">
         <v>15</v>
       </c>
@@ -1498,7 +1514,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="31"/>
     </row>
-    <row r="15" spans="2:7" ht="39">
+    <row r="15" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B15" s="52"/>
       <c r="C15" s="26" t="s">
         <v>17</v>
@@ -1516,7 +1532,7 @@
       </c>
       <c r="G15" s="49"/>
     </row>
-    <row r="16" spans="2:7">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B16" s="53" t="s">
         <v>19</v>
       </c>
@@ -1528,17 +1544,17 @@
       <c r="F16" s="30"/>
       <c r="G16" s="31"/>
     </row>
-    <row r="17" spans="2:7" ht="39">
+    <row r="17" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B17" s="51"/>
       <c r="C17" s="26" t="s">
         <v>21</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="E17" s="16">
         <f>IF(D17="Yes",F17,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="16">
         <f>IF(D17="NA",0,5)</f>
@@ -1546,7 +1562,7 @@
       </c>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B18" s="51"/>
       <c r="C18" s="28" t="s">
         <v>22</v>
@@ -1556,7 +1572,7 @@
       <c r="F18" s="30"/>
       <c r="G18" s="31"/>
     </row>
-    <row r="19" spans="2:7" ht="26.1">
+    <row r="19" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B19" s="51"/>
       <c r="C19" s="26" t="s">
         <v>23</v>
@@ -1574,7 +1590,7 @@
       </c>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="2:7">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B20" s="51"/>
       <c r="C20" s="33" t="s">
         <v>25</v>
@@ -1584,7 +1600,7 @@
       <c r="F20" s="30"/>
       <c r="G20" s="31"/>
     </row>
-    <row r="21" spans="2:7" ht="26.1">
+    <row r="21" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B21" s="52"/>
       <c r="C21" s="26" t="s">
         <v>26</v>
@@ -1602,7 +1618,7 @@
       </c>
       <c r="G21" s="17"/>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B22" s="51" t="s">
         <v>27</v>
       </c>
@@ -1614,7 +1630,7 @@
       <c r="F22" s="30"/>
       <c r="G22" s="31"/>
     </row>
-    <row r="23" spans="2:7" ht="38.450000000000003">
+    <row r="23" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B23" s="51"/>
       <c r="C23" s="26" t="s">
         <v>29</v>
@@ -1632,7 +1648,7 @@
       </c>
       <c r="G23" s="49"/>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B24" s="51"/>
       <c r="C24" s="33" t="s">
         <v>30</v>
@@ -1642,7 +1658,7 @@
       <c r="F24" s="30"/>
       <c r="G24" s="31"/>
     </row>
-    <row r="25" spans="2:7" ht="39">
+    <row r="25" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B25" s="52"/>
       <c r="C25" s="26" t="s">
         <v>31</v>
@@ -1660,7 +1676,7 @@
       </c>
       <c r="G25" s="50"/>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B26" s="53" t="s">
         <v>32</v>
       </c>
@@ -1672,7 +1688,7 @@
       <c r="F26" s="30"/>
       <c r="G26" s="31"/>
     </row>
-    <row r="27" spans="2:7" ht="26.1">
+    <row r="27" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B27" s="51"/>
       <c r="C27" s="26" t="s">
         <v>34</v>
@@ -1690,7 +1706,7 @@
       </c>
       <c r="G27" s="49"/>
     </row>
-    <row r="28" spans="2:7">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B28" s="51"/>
       <c r="C28" s="28" t="s">
         <v>35</v>
@@ -1700,7 +1716,7 @@
       <c r="F28" s="30"/>
       <c r="G28" s="31"/>
     </row>
-    <row r="29" spans="2:7" ht="21" customHeight="1">
+    <row r="29" spans="2:7" ht="21" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="51"/>
       <c r="C29" s="26" t="s">
         <v>36</v>
@@ -1718,7 +1734,7 @@
       </c>
       <c r="G29" s="17"/>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B30" s="51"/>
       <c r="C30" s="33" t="s">
         <v>37</v>
@@ -1728,7 +1744,7 @@
       <c r="F30" s="30"/>
       <c r="G30" s="31"/>
     </row>
-    <row r="31" spans="2:7" ht="39">
+    <row r="31" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B31" s="51"/>
       <c r="C31" s="26" t="s">
         <v>38</v>
@@ -1746,7 +1762,7 @@
       </c>
       <c r="G31" s="17"/>
     </row>
-    <row r="32" spans="2:7">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B32" s="53" t="s">
         <v>39</v>
       </c>
@@ -1758,7 +1774,7 @@
       <c r="F32" s="30"/>
       <c r="G32" s="31"/>
     </row>
-    <row r="33" spans="2:7" ht="39">
+    <row r="33" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B33" s="52"/>
       <c r="C33" s="26" t="s">
         <v>41</v>
@@ -1776,7 +1792,7 @@
       </c>
       <c r="G33" s="17"/>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B34" s="51" t="s">
         <v>42</v>
       </c>
@@ -1788,7 +1804,7 @@
       <c r="F34" s="30"/>
       <c r="G34" s="31"/>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B35" s="52"/>
       <c r="C35" s="26" t="s">
         <v>44</v>
@@ -1806,7 +1822,7 @@
       </c>
       <c r="G35" s="17"/>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B36" s="53" t="s">
         <v>45</v>
       </c>
@@ -1818,7 +1834,7 @@
       <c r="F36" s="30"/>
       <c r="G36" s="31"/>
     </row>
-    <row r="37" spans="2:7" ht="26.1">
+    <row r="37" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B37" s="51"/>
       <c r="C37" s="26" t="s">
         <v>47</v>
@@ -1836,7 +1852,7 @@
       </c>
       <c r="G37" s="17"/>
     </row>
-    <row r="38" spans="2:7">
+    <row r="38" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B38" s="51"/>
       <c r="C38" s="33" t="s">
         <v>48</v>
@@ -1846,7 +1862,7 @@
       <c r="F38" s="30"/>
       <c r="G38" s="31"/>
     </row>
-    <row r="39" spans="2:7">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B39" s="52"/>
       <c r="C39" s="26" t="s">
         <v>49</v>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G39" s="49"/>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B40" s="53" t="s">
         <v>50</v>
       </c>
@@ -1876,7 +1892,7 @@
       <c r="F40" s="30"/>
       <c r="G40" s="31"/>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B41" s="51"/>
       <c r="C41" s="27" t="s">
         <v>52</v>
@@ -1894,7 +1910,7 @@
       </c>
       <c r="G41" s="17"/>
     </row>
-    <row r="42" spans="2:7" ht="26.1">
+    <row r="42" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B42" s="51"/>
       <c r="C42" s="26" t="s">
         <v>53</v>
@@ -1912,7 +1928,7 @@
       </c>
       <c r="G42" s="17"/>
     </row>
-    <row r="43" spans="2:7">
+    <row r="43" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B43" s="51"/>
       <c r="C43" s="33" t="s">
         <v>54</v>
@@ -1931,7 +1947,7 @@
       </c>
       <c r="G43" s="31"/>
     </row>
-    <row r="44" spans="2:7">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B44" s="51"/>
       <c r="C44" s="26" t="s">
         <v>55</v>
@@ -1943,7 +1959,7 @@
       <c r="F44" s="16"/>
       <c r="G44" s="17"/>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B45" s="51"/>
       <c r="C45" s="26" t="s">
         <v>56</v>
@@ -1955,7 +1971,7 @@
       <c r="F45" s="16"/>
       <c r="G45" s="17"/>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B46" s="51"/>
       <c r="C46" s="26" t="s">
         <v>57</v>
@@ -1967,7 +1983,7 @@
       <c r="F46" s="16"/>
       <c r="G46" s="17"/>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B47" s="51"/>
       <c r="C47" s="26" t="s">
         <v>58</v>
@@ -1979,7 +1995,7 @@
       <c r="F47" s="16"/>
       <c r="G47" s="17"/>
     </row>
-    <row r="48" spans="2:7">
+    <row r="48" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B48" s="51"/>
       <c r="C48" s="26" t="s">
         <v>59</v>
@@ -1991,7 +2007,7 @@
       <c r="F48" s="16"/>
       <c r="G48" s="17"/>
     </row>
-    <row r="49" spans="2:7">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B49" s="51"/>
       <c r="C49" s="27" t="s">
         <v>60</v>
@@ -2003,7 +2019,7 @@
       <c r="F49" s="16"/>
       <c r="G49" s="17"/>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B50" s="51"/>
       <c r="C50" s="27" t="s">
         <v>61</v>
@@ -2015,7 +2031,7 @@
       <c r="F50" s="16"/>
       <c r="G50" s="17"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B51" s="51"/>
       <c r="C51" s="27" t="s">
         <v>62</v>
@@ -2027,7 +2043,7 @@
       <c r="F51" s="16"/>
       <c r="G51" s="17"/>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B52" s="51"/>
       <c r="C52" s="26" t="s">
         <v>64</v>
@@ -2039,7 +2055,7 @@
       <c r="F52" s="16"/>
       <c r="G52" s="17"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B53" s="51"/>
       <c r="C53" s="27" t="s">
         <v>65</v>
@@ -2051,7 +2067,7 @@
       <c r="F53" s="16"/>
       <c r="G53" s="17"/>
     </row>
-    <row r="54" spans="2:7">
+    <row r="54" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B54" s="51"/>
       <c r="C54" s="26" t="s">
         <v>59</v>
@@ -2063,7 +2079,7 @@
       <c r="F54" s="16"/>
       <c r="G54" s="17"/>
     </row>
-    <row r="55" spans="2:7">
+    <row r="55" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B55" s="51"/>
       <c r="C55" s="26" t="s">
         <v>66</v>
@@ -2075,7 +2091,7 @@
       <c r="F55" s="16"/>
       <c r="G55" s="17"/>
     </row>
-    <row r="56" spans="2:7">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B56" s="51"/>
       <c r="C56" s="27" t="s">
         <v>67</v>
@@ -2087,7 +2103,7 @@
       <c r="F56" s="16"/>
       <c r="G56" s="17"/>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B57" s="51"/>
       <c r="C57" s="26" t="s">
         <v>68</v>
@@ -2099,7 +2115,7 @@
       <c r="F57" s="16"/>
       <c r="G57" s="17"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B58" s="51"/>
       <c r="C58" s="26" t="s">
         <v>69</v>
@@ -2111,7 +2127,7 @@
       <c r="F58" s="16"/>
       <c r="G58" s="17"/>
     </row>
-    <row r="59" spans="2:7">
+    <row r="59" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B59" s="51"/>
       <c r="C59" s="26" t="s">
         <v>70</v>
@@ -2123,7 +2139,7 @@
       <c r="F59" s="16"/>
       <c r="G59" s="17"/>
     </row>
-    <row r="60" spans="2:7">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B60" s="52"/>
       <c r="C60" s="27" t="s">
         <v>71</v>
@@ -2135,7 +2151,7 @@
       <c r="F60" s="16"/>
       <c r="G60" s="17"/>
     </row>
-    <row r="61" spans="2:7">
+    <row r="61" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B61" s="41" t="s">
         <v>72</v>
       </c>
@@ -2151,7 +2167,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="62" spans="2:7">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B62" s="41" t="s">
         <v>75</v>
       </c>
@@ -2167,7 +2183,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="63" spans="2:7">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B63" s="34"/>
       <c r="C63" s="14"/>
       <c r="D63" s="15"/>
@@ -2175,7 +2191,7 @@
       <c r="F63" s="16"/>
       <c r="G63" s="17"/>
     </row>
-    <row r="64" spans="2:7">
+    <row r="64" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B64" s="34"/>
       <c r="C64" s="14"/>
       <c r="D64" s="15"/>
@@ -2183,13 +2199,13 @@
       <c r="F64" s="16"/>
       <c r="G64" s="17"/>
     </row>
-    <row r="65" spans="2:7" s="38" customFormat="1">
+    <row r="65" spans="2:7" s="38" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B65" s="35"/>
       <c r="C65" s="35"/>
       <c r="D65" s="36"/>
       <c r="E65" s="18">
         <f>SUM(E14:E64)</f>
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F65" s="18">
         <f>SUM(F14:F64)</f>
@@ -2197,13 +2213,13 @@
       </c>
       <c r="G65" s="37"/>
     </row>
-    <row r="66" spans="2:7" s="38" customFormat="1">
+    <row r="66" spans="2:7" s="38" customFormat="1" x14ac:dyDescent="0.45">
       <c r="E66" s="39" t="s">
         <v>77</v>
       </c>
       <c r="F66" s="40">
         <f>E65/F65</f>
-        <v>0.95454545454545459</v>
+        <v>0.84090909090909094</v>
       </c>
     </row>
   </sheetData>
@@ -2351,7 +2367,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1334CD6C-2CAD-4814-97C6-11C04DAB4CAC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2360,12 +2376,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F5C919E-22FB-4185-9268-AAF266484BC8}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>78</v>
@@ -2386,7 +2402,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
@@ -2409,7 +2425,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
         <v>90</v>
       </c>
@@ -2426,7 +2442,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="5" t="s">
         <v>94</v>
       </c>
@@ -2437,7 +2453,7 @@
       <c r="F4" s="8"/>
       <c r="G4" s="9"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
         <v>95</v>
       </c>
